--- a/data/liquidacion_final.xlsx
+++ b/data/liquidacion_final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/03 Marzo/Liquidacióncvs/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="970" documentId="8_{B4C009C8-9220-4C9C-A445-506C3CDC0C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F3131C42-E3C6-4348-82E2-7334BC73F4D9}"/>
+  <xr:revisionPtr revIDLastSave="976" documentId="8_{B4C009C8-9220-4C9C-A445-506C3CDC0C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1907072E-E40E-42AE-828E-19FC2289DB3F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F96EC60D-8A4F-416C-B913-DA3C0AB122B4}"/>
   </bookViews>
@@ -65822,7 +65822,7 @@
         <v>46084</v>
       </c>
       <c r="B2505" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C2505">
         <v>10352328141</v>
@@ -66810,7 +66810,7 @@
         <v>46083</v>
       </c>
       <c r="B2543" t="s">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="C2543">
         <v>1037603803</v>

--- a/data/liquidacion_final.xlsx
+++ b/data/liquidacion_final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/03 Marzo/Liquidacióncvs/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="976" documentId="8_{B4C009C8-9220-4C9C-A445-506C3CDC0C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1907072E-E40E-42AE-828E-19FC2289DB3F}"/>
+  <xr:revisionPtr revIDLastSave="979" documentId="8_{B4C009C8-9220-4C9C-A445-506C3CDC0C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5805AD19-FBC5-4BB7-AB5B-3F333EBED07C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F96EC60D-8A4F-416C-B913-DA3C0AB122B4}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10404" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10406" uniqueCount="95">
   <si>
     <t>Sucursal</t>
   </si>
@@ -362,11 +362,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -701,7 +704,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D750F336-D965-4F10-8ECD-FE069CE0072F}">
-  <dimension ref="A1:H2612"/>
+  <dimension ref="A1:H2613"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="16.28515625" bestFit="1" customWidth="1"/>
@@ -68361,6 +68364,20 @@
       </c>
       <c r="H2612" s="3"/>
     </row>
+    <row r="2613" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2613" s="2">
+        <v>46091</v>
+      </c>
+      <c r="B2613" t="s">
+        <v>38</v>
+      </c>
+      <c r="F2613" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G2613">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H2612" xr:uid="{D750F336-D965-4F10-8ECD-FE069CE0072F}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/liquidacion_final.xlsx
+++ b/data/liquidacion_final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/03 Marzo/Liquidacióncvs/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="979" documentId="8_{B4C009C8-9220-4C9C-A445-506C3CDC0C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5805AD19-FBC5-4BB7-AB5B-3F333EBED07C}"/>
+  <xr:revisionPtr revIDLastSave="982" documentId="8_{B4C009C8-9220-4C9C-A445-506C3CDC0C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87A35120-AC21-4C32-9307-BB0FCC002760}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F96EC60D-8A4F-416C-B913-DA3C0AB122B4}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10406" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10408" uniqueCount="95">
   <si>
     <t>Sucursal</t>
   </si>
@@ -704,7 +704,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D750F336-D965-4F10-8ECD-FE069CE0072F}">
-  <dimension ref="A1:H2613"/>
+  <dimension ref="A1:H2614"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="16.28515625" bestFit="1" customWidth="1"/>
@@ -68378,6 +68378,20 @@
         <v>10</v>
       </c>
     </row>
+    <row r="2614" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2614" s="2">
+        <v>46087</v>
+      </c>
+      <c r="B2614" t="s">
+        <v>85</v>
+      </c>
+      <c r="F2614" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G2614">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H2612" xr:uid="{D750F336-D965-4F10-8ECD-FE069CE0072F}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/liquidacion_final.xlsx
+++ b/data/liquidacion_final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/03 Marzo/Liquidacióncvs/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="991" documentId="8_{B4C009C8-9220-4C9C-A445-506C3CDC0C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD327590-EB46-4854-B18A-DA77DBEDB495}"/>
+  <xr:revisionPtr revIDLastSave="1007" documentId="8_{B4C009C8-9220-4C9C-A445-506C3CDC0C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8498A4E2-EC1C-4397-8BA9-24036A8A8DD1}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F96EC60D-8A4F-416C-B913-DA3C0AB122B4}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Hoja2" sheetId="3" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja2!$A$1:$H$2613</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja2!$A$1:$H$3644</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -11874,7 +11874,7 @@
         <v>46085</v>
       </c>
       <c r="B430" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="C430">
         <v>43262406</v>
@@ -18504,7 +18504,7 @@
         <v>46092</v>
       </c>
       <c r="B685" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="C685">
         <v>1017250353</v>
@@ -22170,7 +22170,7 @@
         <v>46092</v>
       </c>
       <c r="B826" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="C826">
         <v>1017250353</v>
@@ -61092,7 +61092,7 @@
         <v>46083</v>
       </c>
       <c r="B2323" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="C2323">
         <v>1017250353</v>
@@ -68996,7 +68996,7 @@
         <v>46092</v>
       </c>
       <c r="B2627" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="C2627">
         <v>1017250353</v>
@@ -80904,7 +80904,7 @@
         <v>46092</v>
       </c>
       <c r="B3085" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="C3085">
         <v>1017250353</v>
@@ -91980,7 +91980,7 @@
         <v>46084</v>
       </c>
       <c r="B3511" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C3511">
         <v>10352328141</v>
@@ -93748,7 +93748,7 @@
         <v>46083</v>
       </c>
       <c r="B3579" t="s">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="C3579">
         <v>1037603803</v>
@@ -95160,7 +95160,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H2613" xr:uid="{D750F336-D965-4F10-8ECD-FE069CE0072F}"/>
+  <autoFilter ref="A1:H3644" xr:uid="{D750F336-D965-4F10-8ECD-FE069CE0072F}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
